--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118506740</v>
       </c>
       <c r="B2" t="n">
-        <v>91783</v>
+        <v>91790</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121271712</v>
       </c>
       <c r="B3" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>121271738</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271712</v>
+        <v>121271738</v>
       </c>
       <c r="B3" t="n">
-        <v>91973</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690396</v>
+        <v>690522</v>
       </c>
       <c r="R3" t="n">
-        <v>7333133</v>
+        <v>7333041</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271738</v>
+        <v>121271712</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +908,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690522</v>
+        <v>690396</v>
       </c>
       <c r="R4" t="n">
-        <v>7333041</v>
+        <v>7333133</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,6 +987,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271738</v>
+        <v>121271712</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>91986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +793,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690522</v>
+        <v>690396</v>
       </c>
       <c r="R3" t="n">
-        <v>7333041</v>
+        <v>7333133</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271712</v>
+        <v>121271738</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,34 +903,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690396</v>
+        <v>690522</v>
       </c>
       <c r="R4" t="n">
-        <v>7333133</v>
+        <v>7333041</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271712</v>
+        <v>121271738</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690396</v>
+        <v>690522</v>
       </c>
       <c r="R3" t="n">
-        <v>7333133</v>
+        <v>7333041</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271738</v>
+        <v>121271712</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +908,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690522</v>
+        <v>690396</v>
       </c>
       <c r="R4" t="n">
-        <v>7333041</v>
+        <v>7333133</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,6 +987,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271738</v>
+        <v>121271712</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +793,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690522</v>
+        <v>690396</v>
       </c>
       <c r="R3" t="n">
-        <v>7333041</v>
+        <v>7333133</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271712</v>
+        <v>121271738</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,34 +903,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690396</v>
+        <v>690522</v>
       </c>
       <c r="R4" t="n">
-        <v>7333133</v>
+        <v>7333041</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271712</v>
+        <v>121271738</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690396</v>
+        <v>690522</v>
       </c>
       <c r="R3" t="n">
-        <v>7333133</v>
+        <v>7333041</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271738</v>
+        <v>121271712</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>91995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,35 +908,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690522</v>
+        <v>690396</v>
       </c>
       <c r="R4" t="n">
-        <v>7333041</v>
+        <v>7333133</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,6 +987,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121271738</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>121271712</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271738</v>
+        <v>121271712</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +793,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690522</v>
+        <v>690396</v>
       </c>
       <c r="R3" t="n">
-        <v>7333041</v>
+        <v>7333133</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121271712</v>
+        <v>121271738</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,34 +903,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690396</v>
+        <v>690522</v>
       </c>
       <c r="R4" t="n">
-        <v>7333133</v>
+        <v>7333041</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>gamla ringhack i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118506740</v>
+        <v>121271712</v>
       </c>
       <c r="B2" t="n">
-        <v>91795</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäddnajavvre, Pi lm</t>
+          <t>Fäddnajaure, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690727</v>
+        <v>690396</v>
       </c>
       <c r="R2" t="n">
-        <v>7332941</v>
+        <v>7333133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,57 +780,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121271712</v>
+        <v>118506740</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fäddnajaure, Pi lm</t>
+          <t>Fäddnajavvre, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690396</v>
+        <v>690727</v>
       </c>
       <c r="R3" t="n">
-        <v>7333133</v>
+        <v>7332941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,12 +884,7 @@
         <v>121271738</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33873-2022 artfynd.xlsx
+++ b/artfynd/A 33873-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121271712</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118506740</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121271738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>